--- a/data/50m_Femenino_Absoluto_Mariposa.xlsx
+++ b/data/50m_Femenino_Absoluto_Mariposa.xlsx
@@ -728,13 +728,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F8" t="str">
-        <v>00:00:32.14</v>
+        <v>00:00:31.77</v>
       </c>
       <c r="G8">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="H8" s="1">
-        <v>46144.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I8" t="str">
         <v>Deportista</v>
@@ -746,10 +746,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L8" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M8" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N8" t="str">
         <v>No</v>
@@ -1027,7 +1027,7 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C15" t="str">
-        <v>DARIS IVANOVA STOYANOVA</v>
+        <v>SOFIA CALABUIG MARTINEZ</v>
       </c>
       <c r="D15">
         <v>2011</v>
@@ -1036,13 +1036,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F15" t="str">
-        <v>00:00:35.06</v>
+        <v>00:00:34.38</v>
       </c>
       <c r="G15">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="H15" s="1">
-        <v>46082.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I15" t="str">
         <v>Deportista</v>
@@ -1054,13 +1054,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L15" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M15" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N15" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="16">
@@ -1071,7 +1071,7 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C16" t="str">
-        <v>SOFIA CALABUIG MARTINEZ</v>
+        <v>DARIS IVANOVA STOYANOVA</v>
       </c>
       <c r="D16">
         <v>2011</v>
@@ -1080,13 +1080,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F16" t="str">
-        <v>00:00:35.38</v>
+        <v>00:00:35.06</v>
       </c>
       <c r="G16">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="H16" s="1">
-        <v>46081.99949074074</v>
+        <v>46082.99949074074</v>
       </c>
       <c r="I16" t="str">
         <v>Deportista</v>
@@ -1104,7 +1104,7 @@
         <v>CASTELLÓN</v>
       </c>
       <c r="N16" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="17">
@@ -1951,22 +1951,22 @@
         <v>100 Mariposa</v>
       </c>
       <c r="C36" t="str">
-        <v>ANGELS REQUENA MARTINEZ</v>
+        <v>ROCIO MARTINEZ GONZALEZ</v>
       </c>
       <c r="D36">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E36" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F36" t="str">
-        <v>00:01:11.49</v>
+        <v>00:01:10.19</v>
       </c>
       <c r="G36">
-        <v>460</v>
+        <v>486</v>
       </c>
       <c r="H36" s="1">
-        <v>46046.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I36" t="str">
         <v>Deportista</v>
@@ -1978,10 +1978,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L36" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M36" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N36" t="str">
         <v>No</v>
@@ -1995,22 +1995,22 @@
         <v>100 Mariposa</v>
       </c>
       <c r="C37" t="str">
-        <v>ROCIO MARTINEZ GONZALEZ</v>
+        <v>ANGELS REQUENA MARTINEZ</v>
       </c>
       <c r="D37">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E37" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F37" t="str">
-        <v>00:01:12.69</v>
+        <v>00:01:11.49</v>
       </c>
       <c r="G37">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="H37" s="1">
-        <v>46145.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I37" t="str">
         <v>Deportista</v>
@@ -2022,10 +2022,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L37" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M37" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Elche</v>
       </c>
       <c r="N37" t="str">
         <v>No</v>
@@ -2039,22 +2039,22 @@
         <v>100 Mariposa</v>
       </c>
       <c r="C38" t="str">
-        <v>APPOLINARIIA KOROLEVA</v>
+        <v>LOLA FERRI BELLVER</v>
       </c>
       <c r="D38">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E38" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F38" t="str">
-        <v>00:01:14.80</v>
+        <v>00:01:11.78</v>
       </c>
       <c r="G38">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="H38" s="1">
-        <v>46145.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I38" t="str">
         <v>Deportista</v>
@@ -2066,10 +2066,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L38" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M38" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N38" t="str">
         <v>No</v>
@@ -2083,19 +2083,19 @@
         <v>100 Mariposa</v>
       </c>
       <c r="C39" t="str">
-        <v>LOLA FERRI BELLVER</v>
+        <v>APPOLINARIIA KOROLEVA</v>
       </c>
       <c r="D39">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E39" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F39" t="str">
-        <v>00:01:14.93</v>
+        <v>00:01:14.80</v>
       </c>
       <c r="G39">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H39" s="1">
         <v>46145.99949074074</v>
@@ -2136,13 +2136,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F40" t="str">
-        <v>00:01:16.06</v>
+        <v>00:01:15.37</v>
       </c>
       <c r="G40">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H40" s="1">
-        <v>46173.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I40" t="str">
         <v>Deportista</v>
@@ -2151,13 +2151,13 @@
         <v>50m</v>
       </c>
       <c r="K40" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L40" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M40" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N40" t="str">
         <v>Sí</v>
@@ -2752,13 +2752,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F54" t="str">
-        <v>00:02:41.86</v>
+        <v>00:02:35.88</v>
       </c>
       <c r="G54">
-        <v>426</v>
+        <v>477</v>
       </c>
       <c r="H54" s="1">
-        <v>46144.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I54" t="str">
         <v>Deportista</v>
@@ -2770,10 +2770,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L54" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M54" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N54" t="str">
         <v>No</v>
